--- a/artfynd/A 49695-2025 artfynd.xlsx
+++ b/artfynd/A 49695-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49695-2025 artfynd.xlsx
+++ b/artfynd/A 49695-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49695-2025 artfynd.xlsx
+++ b/artfynd/A 49695-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49695-2025 artfynd.xlsx
+++ b/artfynd/A 49695-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49695-2025 artfynd.xlsx
+++ b/artfynd/A 49695-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
